--- a/Zinc/7. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
+++ b/Zinc/7. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/6. Sensitivity analyses/Plots of HA SA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/7. Sensitivity analyses/Plots of HA SA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_A79D70068F1AC385E5DB89F45CE0FFA8C6DAC887" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{406D1E06-A3DD-413D-B496-26C1ADC25255}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_A79D70068F1AC385E5DB89F45CE0FFA8C6DAC887" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EEDEE5C-BC10-4D4B-9905-3AED14BA72F8}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HA_Sensitivity_Summary" sheetId="1" r:id="rId1"/>
@@ -81,6 +81,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -110,8 +114,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -127,6 +135,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -453,16 +465,16 @@
       <c r="D2">
         <v>2.0910044354218902E-9</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>-2.2969256159647999</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>0.178798065044177</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="4">
         <v>-1.0183063539365799E-2</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="4">
         <v>7.9261261308044301E-4</v>
       </c>
       <c r="I2">
@@ -482,16 +494,16 @@
       <c r="D3">
         <v>2.05250926605462E-9</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>-2.20748618733003</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>0.17129814097662199</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="4">
         <v>-9.7779593699774802E-3</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="4">
         <v>7.5817549286705797E-4</v>
       </c>
       <c r="I3">
@@ -511,16 +523,16 @@
       <c r="D4">
         <v>2.0335548585161402E-9</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>-2.1234093704021499</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>0.16509100598154</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="4">
         <v>-9.3985840615854709E-3</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="4">
         <v>7.2956132011518695E-4</v>
       </c>
       <c r="I4">
@@ -540,16 +552,16 @@
       <c r="D5">
         <v>2.02746368698319E-9</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>-2.0455484224361902</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.159536664433446</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="4">
         <v>-9.0479426983702798E-3</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="4">
         <v>7.0401180972203296E-4</v>
       </c>
       <c r="I5">
@@ -569,16 +581,16 @@
       <c r="D6">
         <v>2.0323839751535202E-9</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>-1.9731098664247</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>0.154536867691485</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="4">
         <v>-8.7222944360365508E-3</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="4">
         <v>6.8105648666938804E-4</v>
       </c>
       <c r="I6">
@@ -598,16 +610,16 @@
       <c r="D7">
         <v>4.2795329343134598E-8</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
         <v>-10.4071298743988</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>1.29831285102878</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="4">
         <v>-4.8319827740341603E-2</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="4">
         <v>6.2979128912719999E-3</v>
       </c>
       <c r="I7">
@@ -627,16 +639,16 @@
       <c r="D8">
         <v>3.6134836135558603E-8</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>-9.4642354931906407</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>1.10796295916531</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="4">
         <v>-4.3601223948578301E-2</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="4">
         <v>5.3022547957976797E-3</v>
       </c>
       <c r="I8">
@@ -656,16 +668,16 @@
       <c r="D9">
         <v>3.0765410538306997E-8</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>-8.6650223828835902</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>0.95671927867783801</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="4">
         <v>-3.9670822380739601E-2</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="4">
         <v>4.5297259644982999E-3</v>
       </c>
       <c r="I9">
@@ -685,16 +697,16 @@
       <c r="D10">
         <v>2.63209279062287E-8</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>-7.9827694808351399</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>0.83556877742531099</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="4">
         <v>-3.63619084284535E-2</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="4">
         <v>3.9221732941875599E-3</v>
       </c>
       <c r="I10">
@@ -714,16 +726,16 @@
       <c r="D11">
         <v>2.2640174874281199E-8</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>-7.39603429993522</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>0.73721791179364204</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="4">
         <v>-3.3547857250813301E-2</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="4">
         <v>3.4362674114582501E-3</v>
       </c>
       <c r="I11">
@@ -743,16 +755,16 @@
       <c r="D12">
         <v>2.4132528060123E-9</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>-5.2868378485043603</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>0.25319976297859997</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="4">
         <v>-2.37413060946953E-2</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="4">
         <v>1.1675390874692499E-3</v>
       </c>
       <c r="I12">
@@ -772,16 +784,16 @@
       <c r="D13">
         <v>2.1484975372450001E-9</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>-4.98098623724192</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>0.227689860821887</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="4">
         <v>-2.2310971984055902E-2</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="4">
         <v>1.04425771104331E-3</v>
       </c>
       <c r="I13">
@@ -801,16 +813,16 @@
       <c r="D14">
         <v>1.9436084097777798E-9</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>-4.7100805482861396</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>0.206793182653605</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="4">
         <v>-2.10524816134544E-2</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="4">
         <v>9.4425684870037602E-4</v>
       </c>
       <c r="I14">
@@ -830,16 +842,16 @@
       <c r="D15">
         <v>1.77768343895694E-9</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>-4.4687921471841801</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>0.18904868661930699</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="4">
         <v>-1.9937301531557001E-2</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="4">
         <v>8.6011705743599105E-4</v>
       </c>
       <c r="I15">
@@ -859,16 +871,16 @@
       <c r="D16">
         <v>1.63906491433591E-9</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>-4.2523268058930697</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>0.173776581507817</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="4">
         <v>-1.8941152734943199E-2</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="4">
         <v>7.8822734549052103E-4</v>
       </c>
       <c r="I16">
@@ -888,16 +900,16 @@
       <c r="D17">
         <v>6.5134074394583302E-10</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="2">
         <v>-1.90359254289254</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>9.1561424188408902E-2</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="4">
         <v>-8.3689846048214996E-3</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="4">
         <v>4.0734248111386797E-4</v>
       </c>
       <c r="I17">
@@ -917,16 +929,16 @@
       <c r="D18">
         <v>6.1771975275904805E-10</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="2">
         <v>-1.8616728142991299</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>8.7870663153687398E-2</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="4">
         <v>-8.1816581935879196E-3</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="4">
         <v>3.9052438942069898E-4</v>
       </c>
       <c r="I18">
@@ -946,16 +958,16 @@
       <c r="D19">
         <v>5.8475797159751097E-10</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="2">
         <v>-1.82106774004192</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>8.4241282605094406E-2</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="4">
         <v>-8.0003336466076304E-3</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="4">
         <v>3.7405253392069801E-4</v>
       </c>
       <c r="I19">
@@ -975,16 +987,16 @@
       <c r="D20">
         <v>5.54933073585224E-10</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="2">
         <v>-1.78239997475297</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>8.0880065760522493E-2</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="4">
         <v>-7.8278390834113001E-3</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="4">
         <v>3.5882601334178099E-4</v>
       </c>
       <c r="I20">
@@ -1004,16 +1016,16 @@
       <c r="D21">
         <v>5.2780517451752403E-10</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="2">
         <v>-1.7455230569057301</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>7.7759468471927606E-2</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="4">
         <v>-7.6634901097995204E-3</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="4">
         <v>3.4471331585123402E-4</v>
       </c>
       <c r="I21">
@@ -1064,22 +1076,22 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4">
         <v>-8.4136277861148806E-9</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="4">
         <v>9.1446216134893003E-10</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>-2.1292958925115699</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>7.4174979132111907E-2</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="4">
         <v>-9.4259688210671204E-3</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="4">
         <v>3.2792247583532098E-4</v>
       </c>
       <c r="H2">
@@ -1090,22 +1102,22 @@
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4">
         <v>-1.30113421703884E-7</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <v>1.46362689064322E-8</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>-8.7830383062486792</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>0.45553638118558198</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="4">
         <v>-4.0300327949785303E-2</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="4">
         <v>2.1789825238946701E-3</v>
       </c>
       <c r="H3">
@@ -1116,22 +1128,22 @@
       <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="4">
         <v>-2.09028407102734E-8</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>9.0383211238923495E-10</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>-4.7398047174219302</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>9.5845841621420597E-2</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="4">
         <v>-2.1196642791741199E-2</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="4">
         <v>4.3887129745250102E-4</v>
       </c>
       <c r="H4">
@@ -1142,22 +1154,22 @@
       <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="4">
         <v>-9.4026169784137907E-9</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <v>2.63495482766297E-10</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>-1.8228512257784599</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>3.77773893274269E-2</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="4">
         <v>-8.0084611276455692E-3</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="4">
         <v>1.67781894164436E-4</v>
       </c>
       <c r="H5">

--- a/Zinc/7. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
+++ b/Zinc/7. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/7. Sensitivity analyses/Plots of HA SA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_A79D70068F1AC385E5DB89F45CE0FFA8C6DAC887" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EEDEE5C-BC10-4D4B-9905-3AED14BA72F8}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="11_A79D70068F8AAA46F9CB37AACC1DD2A9F862C125" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCF26265-3059-48FB-9B70-D508D96350E7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HA_Sensitivity_Summary" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="19">
   <si>
     <t>Typology</t>
   </si>
@@ -50,40 +50,44 @@
     <t>n</t>
   </si>
   <si>
+    <t>Pooled</t>
+  </si>
+  <si>
+    <t>10-20</t>
+  </si>
+  <si>
+    <t>20-30</t>
+  </si>
+  <si>
+    <t>30-40</t>
+  </si>
+  <si>
+    <t>40-50</t>
+  </si>
+  <si>
+    <t>50-60</t>
+  </si>
+  <si>
+    <t>Perennial</t>
+  </si>
+  <si>
+    <t>Developed Perennial</t>
+  </si>
+  <si>
+    <t>Non-Perennial</t>
+  </si>
+  <si>
     <t>Main Stem</t>
-  </si>
-  <si>
-    <t>10-20</t>
-  </si>
-  <si>
-    <t>20-30</t>
-  </si>
-  <si>
-    <t>30-40</t>
-  </si>
-  <si>
-    <t>40-50</t>
-  </si>
-  <si>
-    <t>50-60</t>
-  </si>
-  <si>
-    <t>NP Tribs</t>
-  </si>
-  <si>
-    <t>P Tribs</t>
-  </si>
-  <si>
-    <t>PD Tribs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -114,12 +118,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -420,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -460,25 +465,25 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>-1.0475041155626699E-8</v>
+        <v>-3.6076752740503499E-8</v>
       </c>
       <c r="D2">
-        <v>2.0910044354218902E-9</v>
+        <v>1.7153620228982901E-8</v>
       </c>
       <c r="E2" s="2">
-        <v>-2.2969256159647999</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0.178798065044177</v>
-      </c>
-      <c r="G2" s="4">
-        <v>-1.0183063539365799E-2</v>
-      </c>
-      <c r="H2" s="4">
-        <v>7.9261261308044301E-4</v>
+        <v>-5.4684449245376801</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.73083877978013101</v>
+      </c>
+      <c r="G2" s="3">
+        <v>-2.48139775297215E-2</v>
+      </c>
+      <c r="H2" s="3">
+        <v>3.45382037189785E-3</v>
       </c>
       <c r="I2">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -489,25 +494,25 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>-9.3492116459107701E-9</v>
+        <v>-2.9815914380499402E-8</v>
       </c>
       <c r="D3">
-        <v>2.05250926605462E-9</v>
+        <v>1.3285492642277599E-8</v>
       </c>
       <c r="E3" s="2">
-        <v>-2.20748618733003</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0.17129814097662199</v>
-      </c>
-      <c r="G3" s="4">
-        <v>-9.7779593699774802E-3</v>
-      </c>
-      <c r="H3" s="4">
-        <v>7.5817549286705797E-4</v>
+        <v>-5.0982496283791603</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.64064797536608697</v>
+      </c>
+      <c r="G3" s="3">
+        <v>-2.3021708535853599E-2</v>
+      </c>
+      <c r="H3" s="3">
+        <v>3.0003956231007501E-3</v>
       </c>
       <c r="I3">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -518,25 +523,25 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>-8.3218082021242297E-9</v>
+        <v>-2.50388224923837E-8</v>
       </c>
       <c r="D4">
-        <v>2.0335548585161402E-9</v>
+        <v>1.04077200586621E-8</v>
       </c>
       <c r="E4" s="2">
-        <v>-2.1234093704021499</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.16509100598154</v>
-      </c>
-      <c r="G4" s="4">
-        <v>-9.3985840615854709E-3</v>
-      </c>
-      <c r="H4" s="4">
-        <v>7.2956132011518695E-4</v>
+        <v>-4.7754025002522802</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.56842553579525701</v>
+      </c>
+      <c r="G4" s="3">
+        <v>-2.1480983171977299E-2</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2.6422000091819E-3</v>
       </c>
       <c r="I4">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -547,25 +552,25 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>-7.38834084997379E-9</v>
+        <v>-2.1384887652970201E-8</v>
       </c>
       <c r="D5">
-        <v>2.02746368698319E-9</v>
+        <v>8.2778786622128006E-9</v>
       </c>
       <c r="E5" s="2">
-        <v>-2.0455484224361902</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0.159536664433446</v>
-      </c>
-      <c r="G5" s="4">
-        <v>-9.0479426983702798E-3</v>
-      </c>
-      <c r="H5" s="4">
-        <v>7.0401180972203296E-4</v>
+        <v>-4.4957153999757598</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.50874936309504903</v>
+      </c>
+      <c r="G5" s="3">
+        <v>-2.0159629447596399E-2</v>
+      </c>
+      <c r="H5" s="3">
+        <v>2.3503025270124201E-3</v>
       </c>
       <c r="I5">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -576,25 +581,25 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>-6.53373707693889E-9</v>
+        <v>-1.85307160906759E-8</v>
       </c>
       <c r="D6">
-        <v>2.0323839751535202E-9</v>
+        <v>6.6773790981265501E-9</v>
       </c>
       <c r="E6" s="2">
-        <v>-1.9731098664247</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0.154536867691485</v>
-      </c>
-      <c r="G6" s="4">
-        <v>-8.7222944360365508E-3</v>
-      </c>
-      <c r="H6" s="4">
-        <v>6.8105648666938804E-4</v>
+        <v>-4.2501581030822599</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.45835686999321101</v>
+      </c>
+      <c r="G6" s="3">
+        <v>-1.9008792086926501E-2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>2.1065822643941499E-3</v>
       </c>
       <c r="I6">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -604,26 +609,26 @@
       <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="C7">
-        <v>-1.81067108736726E-7</v>
-      </c>
-      <c r="D7">
-        <v>4.2795329343134598E-8</v>
-      </c>
-      <c r="E7" s="3">
-        <v>-10.4071298743988</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1.29831285102878</v>
-      </c>
-      <c r="G7" s="4">
-        <v>-4.8319827740341603E-2</v>
-      </c>
-      <c r="H7" s="4">
-        <v>6.2979128912719999E-3</v>
+      <c r="C7" s="3">
+        <v>-2.59794402520408E-8</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2.5467616843368402E-9</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-5.1977275452584797</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.26913625528888202</v>
+      </c>
+      <c r="G7" s="3">
+        <v>-2.3343347975301802E-2</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1.2392982962722799E-3</v>
       </c>
       <c r="I7">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -633,26 +638,26 @@
       <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C8">
-        <v>-1.4889276348610101E-7</v>
-      </c>
-      <c r="D8">
-        <v>3.6134836135558603E-8</v>
+      <c r="C8" s="3">
+        <v>-2.3043787783745001E-8</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2.2680290944176399E-9</v>
       </c>
       <c r="E8" s="2">
-        <v>-9.4642354931906407</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1.10796295916531</v>
-      </c>
-      <c r="G8" s="4">
-        <v>-4.3601223948578301E-2</v>
-      </c>
-      <c r="H8" s="4">
-        <v>5.3022547957976797E-3</v>
+        <v>-4.8977711332511298</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.242751110424405</v>
+      </c>
+      <c r="G8" s="3">
+        <v>-2.19399464350617E-2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1.1116960032879701E-3</v>
       </c>
       <c r="I8">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -662,26 +667,26 @@
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9">
-        <v>-1.2450205447400101E-7</v>
-      </c>
-      <c r="D9">
-        <v>3.0765410538306997E-8</v>
+      <c r="C9" s="3">
+        <v>-2.0622778960989399E-8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2.05229518558538E-9</v>
       </c>
       <c r="E9" s="2">
-        <v>-8.6650223828835902</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0.95671927867783801</v>
-      </c>
-      <c r="G9" s="4">
-        <v>-3.9670822380739601E-2</v>
-      </c>
-      <c r="H9" s="4">
-        <v>4.5297259644982999E-3</v>
+        <v>-4.6310972868172797</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.221114526744563</v>
+      </c>
+      <c r="G9" s="3">
+        <v>-2.07007661074292E-2</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1.00811261190533E-3</v>
       </c>
       <c r="I9">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -691,26 +696,26 @@
       <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C10">
-        <v>-1.05542841467776E-7</v>
-      </c>
-      <c r="D10">
-        <v>2.63209279062287E-8</v>
+      <c r="C10" s="3">
+        <v>-1.8600035025347199E-8</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1.8774808709058E-9</v>
       </c>
       <c r="E10" s="2">
-        <v>-7.9827694808351399</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0.83556877742531099</v>
-      </c>
-      <c r="G10" s="4">
-        <v>-3.63619084284535E-2</v>
-      </c>
-      <c r="H10" s="4">
-        <v>3.9221732941875599E-3</v>
+        <v>-4.3936512233013998</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.20275292891006699</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-1.9603110213823102E-2</v>
+      </c>
+      <c r="H10" s="3">
+        <v>9.2101757101131798E-4</v>
       </c>
       <c r="I10">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -720,26 +725,26 @@
       <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11">
-        <v>-9.05623403548146E-8</v>
-      </c>
-      <c r="D11">
-        <v>2.2640174874281199E-8</v>
+      <c r="C11" s="3">
+        <v>-1.68863203414552E-8</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1.7313585662821099E-9</v>
       </c>
       <c r="E11" s="2">
-        <v>-7.39603429993522</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0.73721791179364204</v>
-      </c>
-      <c r="G11" s="4">
-        <v>-3.3547857250813301E-2</v>
-      </c>
-      <c r="H11" s="4">
-        <v>3.4362674114582501E-3</v>
+        <v>-4.1806452131901803</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0.18695391942728001</v>
+      </c>
+      <c r="G11" s="3">
+        <v>-1.8622718306026499E-2</v>
+      </c>
+      <c r="H11" s="3">
+        <v>8.4662572034837995E-4</v>
       </c>
       <c r="I11">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -749,26 +754,26 @@
       <c r="B12" t="s">
         <v>10</v>
       </c>
-      <c r="C12">
-        <v>-2.58243511074335E-8</v>
-      </c>
-      <c r="D12">
-        <v>2.4132528060123E-9</v>
+      <c r="C12" s="3">
+        <v>-1.01055446407544E-8</v>
+      </c>
+      <c r="D12" s="3">
+        <v>6.2896839237523105E-10</v>
       </c>
       <c r="E12" s="2">
-        <v>-5.2868378485043603</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0.25319976297859997</v>
-      </c>
-      <c r="G12" s="4">
-        <v>-2.37413060946953E-2</v>
-      </c>
-      <c r="H12" s="4">
-        <v>1.1675390874692499E-3</v>
+        <v>-1.8920883590715301</v>
+      </c>
+      <c r="F12" s="4">
+        <v>8.8580283449750205E-2</v>
+      </c>
+      <c r="G12" s="3">
+        <v>-8.3175296697186908E-3</v>
+      </c>
+      <c r="H12" s="3">
+        <v>3.94067968533786E-4</v>
       </c>
       <c r="I12">
-        <v>98</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -778,26 +783,26 @@
       <c r="B13" t="s">
         <v>11</v>
       </c>
-      <c r="C13">
-        <v>-2.2906428905412199E-8</v>
-      </c>
-      <c r="D13">
-        <v>2.1484975372450001E-9</v>
+      <c r="C13" s="3">
+        <v>-9.6622035770715207E-9</v>
+      </c>
+      <c r="D13" s="3">
+        <v>5.9634647887230503E-10</v>
       </c>
       <c r="E13" s="2">
-        <v>-4.98098623724192</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0.227689860821887</v>
-      </c>
-      <c r="G13" s="4">
-        <v>-2.2310971984055902E-2</v>
-      </c>
-      <c r="H13" s="4">
-        <v>1.04425771104331E-3</v>
+        <v>-1.84977609505826</v>
+      </c>
+      <c r="F13" s="4">
+        <v>8.5065800568429398E-2</v>
+      </c>
+      <c r="G13" s="3">
+        <v>-8.1285566170771102E-3</v>
+      </c>
+      <c r="H13" s="3">
+        <v>3.7804723616807902E-4</v>
       </c>
       <c r="I13">
-        <v>98</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -807,26 +812,26 @@
       <c r="B14" t="s">
         <v>12</v>
       </c>
-      <c r="C14">
-        <v>-2.0502028257512799E-8</v>
-      </c>
-      <c r="D14">
-        <v>1.9436084097777798E-9</v>
+      <c r="C14" s="3">
+        <v>-9.2636383285338797E-9</v>
+      </c>
+      <c r="D14" s="3">
+        <v>5.6458421302675805E-10</v>
       </c>
       <c r="E14" s="2">
-        <v>-4.7100805482861396</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0.206793182653605</v>
-      </c>
-      <c r="G14" s="4">
-        <v>-2.10524816134544E-2</v>
-      </c>
-      <c r="H14" s="4">
-        <v>9.4425684870037602E-4</v>
+        <v>-1.80957927744439</v>
+      </c>
+      <c r="F14" s="4">
+        <v>8.1558483850847102E-2</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-7.9491002053322397E-3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>3.62131631672481E-4</v>
       </c>
       <c r="I14">
-        <v>98</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -836,26 +841,26 @@
       <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="C15">
-        <v>-1.8492267724842099E-8</v>
-      </c>
-      <c r="D15">
-        <v>1.77768343895694E-9</v>
+      <c r="C15" s="3">
+        <v>-8.8926392696300007E-9</v>
+      </c>
+      <c r="D15" s="3">
+        <v>5.3584239908581604E-10</v>
       </c>
       <c r="E15" s="2">
-        <v>-4.4687921471841801</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0.18904868661930699</v>
-      </c>
-      <c r="G15" s="4">
-        <v>-1.9937301531557001E-2</v>
-      </c>
-      <c r="H15" s="4">
-        <v>8.6011705743599105E-4</v>
+        <v>-1.7712961466549599</v>
+      </c>
+      <c r="F15" s="4">
+        <v>7.8309582308029299E-2</v>
+      </c>
+      <c r="G15" s="3">
+        <v>-7.7783618081158998E-3</v>
+      </c>
+      <c r="H15" s="3">
+        <v>3.4741583698636998E-4</v>
       </c>
       <c r="I15">
-        <v>98</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -865,26 +870,26 @@
       <c r="B16" t="s">
         <v>14</v>
       </c>
-      <c r="C16">
-        <v>-1.67891275561663E-8</v>
-      </c>
-      <c r="D16">
-        <v>1.63906491433591E-9</v>
+      <c r="C16" s="3">
+        <v>-8.5463591007097602E-9</v>
+      </c>
+      <c r="D16" s="3">
+        <v>5.09698048093002E-10</v>
       </c>
       <c r="E16" s="2">
-        <v>-4.2523268058930697</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0.173776581507817</v>
-      </c>
-      <c r="G16" s="4">
-        <v>-1.8941152734943199E-2</v>
-      </c>
-      <c r="H16" s="4">
-        <v>7.8822734549052103E-4</v>
+        <v>-1.73478136746546</v>
+      </c>
+      <c r="F16" s="4">
+        <v>7.5292739227758795E-2</v>
+      </c>
+      <c r="G16" s="3">
+        <v>-7.6156631357156201E-3</v>
+      </c>
+      <c r="H16" s="3">
+        <v>3.3377399715673001E-4</v>
       </c>
       <c r="I16">
-        <v>98</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -894,26 +899,26 @@
       <c r="B17" t="s">
         <v>10</v>
       </c>
-      <c r="C17">
-        <v>-1.0222310442149499E-8</v>
-      </c>
-      <c r="D17">
-        <v>6.5134074394583302E-10</v>
-      </c>
-      <c r="E17" s="2">
-        <v>-1.90359254289254</v>
-      </c>
-      <c r="F17" s="1">
-        <v>9.1561424188408902E-2</v>
-      </c>
-      <c r="G17" s="4">
-        <v>-8.3689846048214996E-3</v>
-      </c>
-      <c r="H17" s="4">
-        <v>4.0734248111386797E-4</v>
+      <c r="C17" s="3">
+        <v>-1.81067108736726E-7</v>
+      </c>
+      <c r="D17" s="3">
+        <v>4.2795329343134598E-8</v>
+      </c>
+      <c r="E17" s="5">
+        <v>-10.4071298743988</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1.29831285102878</v>
+      </c>
+      <c r="G17" s="3">
+        <v>-4.8319827740341603E-2</v>
+      </c>
+      <c r="H17" s="3">
+        <v>6.2979128912719999E-3</v>
       </c>
       <c r="I17">
-        <v>117</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -923,26 +928,26 @@
       <c r="B18" t="s">
         <v>11</v>
       </c>
-      <c r="C18">
-        <v>-9.7790769227749002E-9</v>
-      </c>
-      <c r="D18">
-        <v>6.1771975275904805E-10</v>
+      <c r="C18" s="3">
+        <v>-1.4889276348610101E-7</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3.6134836135558603E-8</v>
       </c>
       <c r="E18" s="2">
-        <v>-1.8616728142991299</v>
-      </c>
-      <c r="F18" s="1">
-        <v>8.7870663153687398E-2</v>
-      </c>
-      <c r="G18" s="4">
-        <v>-8.1816581935879196E-3</v>
-      </c>
-      <c r="H18" s="4">
-        <v>3.9052438942069898E-4</v>
+        <v>-9.4642354931906407</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1.10796295916531</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-4.3601223948578301E-2</v>
+      </c>
+      <c r="H18" s="3">
+        <v>5.3022547957976797E-3</v>
       </c>
       <c r="I18">
-        <v>117</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -952,26 +957,26 @@
       <c r="B19" t="s">
         <v>12</v>
       </c>
-      <c r="C19">
-        <v>-9.3731717333889195E-9</v>
-      </c>
-      <c r="D19">
-        <v>5.8475797159751097E-10</v>
+      <c r="C19" s="3">
+        <v>-1.2450205447400101E-7</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3.0765410538306997E-8</v>
       </c>
       <c r="E19" s="2">
-        <v>-1.82106774004192</v>
-      </c>
-      <c r="F19" s="1">
-        <v>8.4241282605094406E-2</v>
-      </c>
-      <c r="G19" s="4">
-        <v>-8.0003336466076304E-3</v>
-      </c>
-      <c r="H19" s="4">
-        <v>3.7405253392069801E-4</v>
+        <v>-8.6650223828835902</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0.95671927867783801</v>
+      </c>
+      <c r="G19" s="3">
+        <v>-3.9670822380739601E-2</v>
+      </c>
+      <c r="H19" s="3">
+        <v>4.5297259644982999E-3</v>
       </c>
       <c r="I19">
-        <v>117</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -981,26 +986,26 @@
       <c r="B20" t="s">
         <v>13</v>
       </c>
-      <c r="C20">
-        <v>-8.9954706985650302E-9</v>
-      </c>
-      <c r="D20">
-        <v>5.54933073585224E-10</v>
+      <c r="C20" s="3">
+        <v>-1.05542841467776E-7</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2.63209279062287E-8</v>
       </c>
       <c r="E20" s="2">
-        <v>-1.78239997475297</v>
-      </c>
-      <c r="F20" s="1">
-        <v>8.0880065760522493E-2</v>
-      </c>
-      <c r="G20" s="4">
-        <v>-7.8278390834113001E-3</v>
-      </c>
-      <c r="H20" s="4">
-        <v>3.5882601334178099E-4</v>
+        <v>-7.9827694808351399</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0.83556877742531099</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-3.63619084284535E-2</v>
+      </c>
+      <c r="H20" s="3">
+        <v>3.9221732941875599E-3</v>
       </c>
       <c r="I20">
-        <v>117</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -1010,26 +1015,171 @@
       <c r="B21" t="s">
         <v>14</v>
       </c>
-      <c r="C21">
-        <v>-8.6430550951905695E-9</v>
-      </c>
-      <c r="D21">
-        <v>5.2780517451752403E-10</v>
+      <c r="C21" s="3">
+        <v>-9.05623403548146E-8</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2.2640174874281199E-8</v>
       </c>
       <c r="E21" s="2">
-        <v>-1.7455230569057301</v>
-      </c>
-      <c r="F21" s="1">
-        <v>7.7759468471927606E-2</v>
-      </c>
-      <c r="G21" s="4">
-        <v>-7.6634901097995204E-3</v>
-      </c>
-      <c r="H21" s="4">
-        <v>3.4471331585123402E-4</v>
+        <v>-7.39603429993522</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0.73721791179364204</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-3.3547857250813301E-2</v>
+      </c>
+      <c r="H21" s="3">
+        <v>3.4362674114582501E-3</v>
       </c>
       <c r="I21">
-        <v>117</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="3">
+        <v>-1.10878942315963E-8</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2.0978798305324198E-9</v>
+      </c>
+      <c r="E22" s="2">
+        <v>-2.5064295148316398</v>
+      </c>
+      <c r="F22" s="4">
+        <v>0.19124140695563299</v>
+      </c>
+      <c r="G22" s="3">
+        <v>-1.11291203475194E-2</v>
+      </c>
+      <c r="H22" s="3">
+        <v>8.5085168479103498E-4</v>
+      </c>
+      <c r="I22">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="3">
+        <v>-9.8777229246827901E-9</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2.0577157533547101E-9</v>
+      </c>
+      <c r="E23" s="2">
+        <v>-2.4026591915287798</v>
+      </c>
+      <c r="F23" s="4">
+        <v>0.18206627432500899</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-1.06569384041753E-2</v>
+      </c>
+      <c r="H23" s="3">
+        <v>8.0834568629866604E-4</v>
+      </c>
+      <c r="I23">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="3">
+        <v>-8.7767494823574396E-9</v>
+      </c>
+      <c r="D24" s="3">
+        <v>2.0376978389986999E-9</v>
+      </c>
+      <c r="E24" s="2">
+        <v>-2.3060243294157301</v>
+      </c>
+      <c r="F24" s="4">
+        <v>0.17458996824161099</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-1.0219219980720701E-2</v>
+      </c>
+      <c r="H24" s="3">
+        <v>7.7363932314188403E-4</v>
+      </c>
+      <c r="I24">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="3">
+        <v>-7.7820972319776504E-9</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2.03087174328904E-9</v>
+      </c>
+      <c r="E25" s="2">
+        <v>-2.21700301937488</v>
+      </c>
+      <c r="F25" s="4">
+        <v>0.16796383851668201</v>
+      </c>
+      <c r="G25" s="3">
+        <v>-9.8169453155043107E-3</v>
+      </c>
+      <c r="H25" s="3">
+        <v>7.4297874757992097E-4</v>
+      </c>
+      <c r="I25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="3">
+        <v>-6.8761649871725003E-9</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2.0352660638155902E-9</v>
+      </c>
+      <c r="E26" s="2">
+        <v>-2.1346129607398101</v>
+      </c>
+      <c r="F26" s="4">
+        <v>0.16205700165777001</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-9.4454251907862101E-3</v>
+      </c>
+      <c r="H26" s="3">
+        <v>7.1572250070333699E-4</v>
+      </c>
+      <c r="I26">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1040,11 +1190,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="4" max="4" width="16.08984375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -1076,108 +1223,140 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="4">
-        <v>-8.4136277861148806E-9</v>
-      </c>
-      <c r="C2" s="4">
-        <v>9.1446216134893003E-10</v>
-      </c>
-      <c r="D2" s="3">
-        <v>-2.1292958925115699</v>
+      <c r="B2">
+        <v>-2.6169418671406501E-8</v>
+      </c>
+      <c r="C2">
+        <v>5.2157812691848197E-9</v>
+      </c>
+      <c r="D2" s="2">
+        <v>-4.8175941112454304</v>
       </c>
       <c r="E2" s="1">
-        <v>7.4174979132111907E-2</v>
-      </c>
-      <c r="F2" s="4">
-        <v>-9.4259688210671204E-3</v>
-      </c>
-      <c r="G2" s="4">
-        <v>3.2792247583532098E-4</v>
+        <v>0.26238594078301902</v>
+      </c>
+      <c r="F2" s="3">
+        <v>-2.1697018154415E-2</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1.22581591874153E-3</v>
       </c>
       <c r="H2">
-        <v>635</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="4">
-        <v>-1.30113421703884E-7</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1.46362689064322E-8</v>
-      </c>
-      <c r="D3" s="3">
-        <v>-8.7830383062486792</v>
+      <c r="B3">
+        <v>-2.10264724727155E-8</v>
+      </c>
+      <c r="C3">
+        <v>9.5351391827897302E-10</v>
+      </c>
+      <c r="D3" s="2">
+        <v>-4.6601784803636903</v>
       </c>
       <c r="E3" s="1">
-        <v>0.45553638118558198</v>
-      </c>
-      <c r="F3" s="4">
-        <v>-4.0300327949785303E-2</v>
-      </c>
-      <c r="G3" s="4">
-        <v>2.1789825238946701E-3</v>
+        <v>0.102191894072722</v>
+      </c>
+      <c r="F3" s="3">
+        <v>-2.0841977807528399E-2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>4.6721131160942E-4</v>
       </c>
       <c r="H3">
-        <v>70</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="4">
-        <v>-2.09028407102734E-8</v>
-      </c>
-      <c r="C4" s="4">
-        <v>9.0383211238923495E-10</v>
-      </c>
-      <c r="D4" s="3">
-        <v>-4.7398047174219302</v>
-      </c>
-      <c r="E4" s="1">
-        <v>9.5845841621420597E-2</v>
-      </c>
-      <c r="F4" s="4">
-        <v>-2.1196642791741199E-2</v>
-      </c>
-      <c r="G4" s="4">
-        <v>4.3887129745250102E-4</v>
+      <c r="B4">
+        <v>-9.2940769833399208E-9</v>
+      </c>
+      <c r="C4">
+        <v>2.5445821077355202E-10</v>
+      </c>
+      <c r="D4" s="2">
+        <v>-1.8115042491389199</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.65746007869771E-2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-7.9578422871919106E-3</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.6243580912350301E-4</v>
       </c>
       <c r="H4">
-        <v>490</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="4">
-        <v>-9.4026169784137907E-9</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2.63495482766297E-10</v>
-      </c>
-      <c r="D5" s="3">
-        <v>-1.8228512257784599</v>
+      <c r="B5">
+        <v>-1.30113421703884E-7</v>
+      </c>
+      <c r="C5">
+        <v>1.46362689064322E-8</v>
+      </c>
+      <c r="D5" s="2">
+        <v>-8.7830383062486792</v>
       </c>
       <c r="E5" s="1">
-        <v>3.77773893274269E-2</v>
-      </c>
-      <c r="F5" s="4">
-        <v>-8.0084611276455692E-3</v>
-      </c>
-      <c r="G5" s="4">
-        <v>1.67781894164436E-4</v>
+        <v>0.45553638118558198</v>
+      </c>
+      <c r="F5" s="3">
+        <v>-4.0300327949785303E-2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2.1789825238946701E-3</v>
       </c>
       <c r="H5">
-        <v>585</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>-8.8801257715573396E-9</v>
+      </c>
+      <c r="C6">
+        <v>9.1671091274396205E-10</v>
+      </c>
+      <c r="D6" s="2">
+        <v>-2.3133458031781702</v>
+      </c>
+      <c r="E6" s="1">
+        <v>7.8583455463715299E-2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>-1.0253529847741199E-2</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3.4842368603567401E-4</v>
+      </c>
+      <c r="H6">
+        <v>635</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{db3dbd43-4c4b-4544-9f8a-0553f9f5f25e}" enabled="0" method="" siteId="{db3dbd43-4c4b-4544-9f8a-0553f9f5f25e}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/Zinc/7. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
+++ b/Zinc/7. Sensitivity analyses/Plots of HA SA/HA_Sensitivity_Summary.xlsx
@@ -42,34 +42,34 @@
     <t xml:space="preserve">n</t>
   </si>
   <si>
+    <t xml:space="preserve">Developed Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50-60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Perennial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pooled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40-50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50-60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Perennial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem</t>
   </si>
 </sst>
 </file>
@@ -435,25 +435,25 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0000000360767527405035</v>
+        <v>-0.0000000101055446407544</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000000171536202289829</v>
+        <v>0.000000000628968392375231</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.46844492453768</v>
+        <v>-1.89208835907153</v>
       </c>
       <c r="F2" t="n">
-        <v>0.730838779780131</v>
+        <v>0.0885802834497502</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0248139775297215</v>
+        <v>-0.00831752966971869</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00345382037189785</v>
+        <v>0.000394067968533786</v>
       </c>
       <c r="I2" t="n">
-        <v>30</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3">
@@ -464,25 +464,25 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0000000298159143804994</v>
+        <v>-0.00000000966220357707152</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000000132854926422776</v>
+        <v>0.000000000596346478872305</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.09824962837916</v>
+        <v>-1.84977609505826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.640647975366087</v>
+        <v>0.0850658005684294</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0230217085358536</v>
+        <v>-0.00812855661707711</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00300039562310075</v>
+        <v>0.000378047236168079</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4">
@@ -493,25 +493,25 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0000000250388224923837</v>
+        <v>-0.00000000926363832853388</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000000104077200586621</v>
+        <v>0.000000000564584213026758</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.77540250025228</v>
+        <v>-1.80957927744439</v>
       </c>
       <c r="F4" t="n">
-        <v>0.568425535795257</v>
+        <v>0.0815584838508471</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0214809831719773</v>
+        <v>-0.00794910020533224</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0026422000091819</v>
+        <v>0.000362131631672481</v>
       </c>
       <c r="I4" t="n">
-        <v>30</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5">
@@ -522,25 +522,25 @@
         <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0000000213848876529702</v>
+        <v>-0.00000000889263926963</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0000000082778786622128</v>
+        <v>0.000000000535842399085816</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.49571539997576</v>
+        <v>-1.77129614665496</v>
       </c>
       <c r="F5" t="n">
-        <v>0.508749363095049</v>
+        <v>0.0783095823080293</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0201596294475964</v>
+        <v>-0.0077783618081159</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00235030252701242</v>
+        <v>0.00034741583698637</v>
       </c>
       <c r="I5" t="n">
-        <v>30</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6">
@@ -551,25 +551,25 @@
         <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0000000185307160906759</v>
+        <v>-0.00000000854635910070976</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00000000667737909812655</v>
+        <v>0.000000000509698048093002</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.25015810308226</v>
+        <v>-1.73478136746546</v>
       </c>
       <c r="F6" t="n">
-        <v>0.458356869993211</v>
+        <v>0.0752927392277588</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0190087920869265</v>
+        <v>-0.00761566313571562</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00210658226439415</v>
+        <v>0.00033377399715673</v>
       </c>
       <c r="I6" t="n">
-        <v>30</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -580,25 +580,25 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0000000259794402520408</v>
+        <v>-0.0000000110878942315963</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00000000254676168433684</v>
+        <v>0.00000000209787983053242</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.19772754525848</v>
+        <v>-2.50642951483164</v>
       </c>
       <c r="F7" t="n">
-        <v>0.269136255288882</v>
+        <v>0.191241406955633</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0233433479753018</v>
+        <v>-0.0111291203475194</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00123929829627228</v>
+        <v>0.000850851684791035</v>
       </c>
       <c r="I7" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8">
@@ -609,25 +609,25 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.000000023043787783745</v>
+        <v>-0.00000000987772292468279</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00000000226802909441764</v>
+        <v>0.00000000205771575335471</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.89777113325113</v>
+        <v>-2.40265919152878</v>
       </c>
       <c r="F8" t="n">
-        <v>0.242751110424405</v>
+        <v>0.182066274325009</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0219399464350617</v>
+        <v>-0.0106569384041753</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00111169600328797</v>
+        <v>0.000808345686298666</v>
       </c>
       <c r="I8" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9">
@@ -638,25 +638,25 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0000000206227789609894</v>
+        <v>-0.00000000877674948235744</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00000000205229518558538</v>
+        <v>0.0000000020376978389987</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.63109728681728</v>
+        <v>-2.30602432941573</v>
       </c>
       <c r="F9" t="n">
-        <v>0.221114526744563</v>
+        <v>0.174589968241611</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0207007661074292</v>
+        <v>-0.0102192199807207</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00100811261190533</v>
+        <v>0.000773639323141884</v>
       </c>
       <c r="I9" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10">
@@ -667,25 +667,25 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0000000186000350253472</v>
+        <v>-0.00000000778209723197765</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0000000018774808709058</v>
+        <v>0.00000000203087174328904</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3936512233014</v>
+        <v>-2.21700301937488</v>
       </c>
       <c r="F10" t="n">
-        <v>0.202752928910067</v>
+        <v>0.167963838516682</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0196031102138231</v>
+        <v>-0.00981694531550431</v>
       </c>
       <c r="H10" t="n">
-        <v>0.000921017571011318</v>
+        <v>0.000742978747579921</v>
       </c>
       <c r="I10" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
@@ -696,25 +696,25 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0000000168863203414552</v>
+        <v>-0.0000000068761649871725</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00000000173135856628211</v>
+        <v>0.00000000203526606381559</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.18064521319018</v>
+        <v>-2.13461296073981</v>
       </c>
       <c r="F11" t="n">
-        <v>0.18695391942728</v>
+        <v>0.16205700165777</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0186227183060265</v>
+        <v>-0.00944542519078621</v>
       </c>
       <c r="H11" t="n">
-        <v>0.00084662572034838</v>
+        <v>0.000715722500703337</v>
       </c>
       <c r="I11" t="n">
-        <v>93</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
@@ -725,25 +725,25 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0000000101055446407544</v>
+        <v>-0.000000181067108736726</v>
       </c>
       <c r="D12" t="n">
-        <v>0.000000000628968392375231</v>
+        <v>0.0000000427953293431346</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.89208835907153</v>
+        <v>-10.4071298743988</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0885802834497502</v>
+        <v>1.29831285102878</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.00831752966971869</v>
+        <v>-0.0483198277403416</v>
       </c>
       <c r="H12" t="n">
-        <v>0.000394067968533786</v>
+        <v>0.006297912891272</v>
       </c>
       <c r="I12" t="n">
-        <v>122</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -754,25 +754,25 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.00000000966220357707152</v>
+        <v>-0.000000148892763486101</v>
       </c>
       <c r="D13" t="n">
-        <v>0.000000000596346478872305</v>
+        <v>0.0000000361348361355586</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.84977609505826</v>
+        <v>-9.46423549319064</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0850658005684294</v>
+        <v>1.10796295916531</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.00812855661707711</v>
+        <v>-0.0436012239485783</v>
       </c>
       <c r="H13" t="n">
-        <v>0.000378047236168079</v>
+        <v>0.00530225479579768</v>
       </c>
       <c r="I13" t="n">
-        <v>122</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.00000000926363832853388</v>
+        <v>-0.000000124502054474001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.000000000564584213026758</v>
+        <v>0.000000030765410538307</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.80957927744439</v>
+        <v>-8.66502238288359</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0815584838508471</v>
+        <v>0.956719278677838</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.00794910020533224</v>
+        <v>-0.0396708223807396</v>
       </c>
       <c r="H14" t="n">
-        <v>0.000362131631672481</v>
+        <v>0.0045297259644983</v>
       </c>
       <c r="I14" t="n">
-        <v>122</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -812,25 +812,25 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.00000000889263926963</v>
+        <v>-0.000000105542841467776</v>
       </c>
       <c r="D15" t="n">
-        <v>0.000000000535842399085816</v>
+        <v>0.0000000263209279062287</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.77129614665496</v>
+        <v>-7.98276948083514</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0783095823080293</v>
+        <v>0.835568777425311</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0077783618081159</v>
+        <v>-0.0363619084284535</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00034741583698637</v>
+        <v>0.00392217329418756</v>
       </c>
       <c r="I15" t="n">
-        <v>122</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -841,25 +841,25 @@
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.00000000854635910070976</v>
+        <v>-0.0000000905623403548146</v>
       </c>
       <c r="D16" t="n">
-        <v>0.000000000509698048093002</v>
+        <v>0.0000000226401748742812</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.73478136746546</v>
+        <v>-7.39603429993522</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0752927392277588</v>
+        <v>0.737217911793642</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.00761566313571562</v>
+        <v>-0.0335478572508133</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00033377399715673</v>
+        <v>0.00343626741145825</v>
       </c>
       <c r="I16" t="n">
-        <v>122</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -870,25 +870,25 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.000000181067108736726</v>
+        <v>-0.0000000259794402520408</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0000000427953293431346</v>
+        <v>0.00000000254676168433684</v>
       </c>
       <c r="E17" t="n">
-        <v>-10.4071298743988</v>
+        <v>-5.19772754525848</v>
       </c>
       <c r="F17" t="n">
-        <v>1.29831285102878</v>
+        <v>0.269136255288882</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0483198277403416</v>
+        <v>-0.0233433479753018</v>
       </c>
       <c r="H17" t="n">
-        <v>0.006297912891272</v>
+        <v>0.00123929829627228</v>
       </c>
       <c r="I17" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18">
@@ -899,25 +899,25 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.000000148892763486101</v>
+        <v>-0.000000023043787783745</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0000000361348361355586</v>
+        <v>0.00000000226802909441764</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.46423549319064</v>
+        <v>-4.89777113325113</v>
       </c>
       <c r="F18" t="n">
-        <v>1.10796295916531</v>
+        <v>0.242751110424405</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0436012239485783</v>
+        <v>-0.0219399464350617</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00530225479579768</v>
+        <v>0.00111169600328797</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
@@ -928,25 +928,25 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.000000124502054474001</v>
+        <v>-0.0000000206227789609894</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000000030765410538307</v>
+        <v>0.00000000205229518558538</v>
       </c>
       <c r="E19" t="n">
-        <v>-8.66502238288359</v>
+        <v>-4.63109728681728</v>
       </c>
       <c r="F19" t="n">
-        <v>0.956719278677838</v>
+        <v>0.221114526744563</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0396708223807396</v>
+        <v>-0.0207007661074292</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0045297259644983</v>
+        <v>0.00100811261190533</v>
       </c>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -957,25 +957,25 @@
         <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.000000105542841467776</v>
+        <v>-0.0000000186000350253472</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0000000263209279062287</v>
+        <v>0.0000000018774808709058</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.98276948083514</v>
+        <v>-4.3936512233014</v>
       </c>
       <c r="F20" t="n">
-        <v>0.835568777425311</v>
+        <v>0.202752928910067</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0363619084284535</v>
+        <v>-0.0196031102138231</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00392217329418756</v>
+        <v>0.000921017571011318</v>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21">
@@ -986,25 +986,25 @@
         <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0000000905623403548146</v>
+        <v>-0.0000000168863203414552</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0000000226401748742812</v>
+        <v>0.00000000173135856628211</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.39603429993522</v>
+        <v>-4.18064521319018</v>
       </c>
       <c r="F21" t="n">
-        <v>0.737217911793642</v>
+        <v>0.18695391942728</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0335478572508133</v>
+        <v>-0.0186227183060265</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00343626741145825</v>
+        <v>0.00084662572034838</v>
       </c>
       <c r="I21" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22">
@@ -1015,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0000000110878942315963</v>
+        <v>-0.0000000360767527405035</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00000000209787983053242</v>
+        <v>0.0000000171536202289829</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.50642951483164</v>
+        <v>-5.46844492453768</v>
       </c>
       <c r="F22" t="n">
-        <v>0.191241406955633</v>
+        <v>0.730838779780131</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0111291203475194</v>
+        <v>-0.0248139775297215</v>
       </c>
       <c r="H22" t="n">
-        <v>0.000850851684791035</v>
+        <v>0.00345382037189785</v>
       </c>
       <c r="I22" t="n">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -1044,25 +1044,25 @@
         <v>11</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.00000000987772292468279</v>
+        <v>-0.0000000298159143804994</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00000000205771575335471</v>
+        <v>0.0000000132854926422776</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.40265919152878</v>
+        <v>-5.09824962837916</v>
       </c>
       <c r="F23" t="n">
-        <v>0.182066274325009</v>
+        <v>0.640647975366087</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0106569384041753</v>
+        <v>-0.0230217085358536</v>
       </c>
       <c r="H23" t="n">
-        <v>0.000808345686298666</v>
+        <v>0.00300039562310075</v>
       </c>
       <c r="I23" t="n">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -1073,25 +1073,25 @@
         <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.00000000877674948235744</v>
+        <v>-0.0000000250388224923837</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0000000020376978389987</v>
+        <v>0.0000000104077200586621</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.30602432941573</v>
+        <v>-4.77540250025228</v>
       </c>
       <c r="F24" t="n">
-        <v>0.174589968241611</v>
+        <v>0.568425535795257</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0102192199807207</v>
+        <v>-0.0214809831719773</v>
       </c>
       <c r="H24" t="n">
-        <v>0.000773639323141884</v>
+        <v>0.0026422000091819</v>
       </c>
       <c r="I24" t="n">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -1102,25 +1102,25 @@
         <v>13</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.00000000778209723197765</v>
+        <v>-0.0000000213848876529702</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00000000203087174328904</v>
+        <v>0.0000000082778786622128</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.21700301937488</v>
+        <v>-4.49571539997576</v>
       </c>
       <c r="F25" t="n">
-        <v>0.167963838516682</v>
+        <v>0.508749363095049</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.00981694531550431</v>
+        <v>-0.0201596294475964</v>
       </c>
       <c r="H25" t="n">
-        <v>0.000742978747579921</v>
+        <v>0.00235030252701242</v>
       </c>
       <c r="I25" t="n">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -1131,25 +1131,25 @@
         <v>14</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0000000068761649871725</v>
+        <v>-0.0000000185307160906759</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00000000203526606381559</v>
+        <v>0.00000000667737909812655</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.13461296073981</v>
+        <v>-4.25015810308226</v>
       </c>
       <c r="F26" t="n">
-        <v>0.16205700165777</v>
+        <v>0.458356869993211</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.00944542519078621</v>
+        <v>-0.0190087920869265</v>
       </c>
       <c r="H26" t="n">
-        <v>0.000715722500703337</v>
+        <v>0.00210658226439415</v>
       </c>
       <c r="I26" t="n">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1194,25 +1194,25 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.0000000261694186714065</v>
+        <v>-0.00000000929407698333992</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00000000521578126918482</v>
+        <v>0.000000000254458210773552</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.81759411124543</v>
+        <v>-1.81150424913892</v>
       </c>
       <c r="E2" t="n">
-        <v>0.262385940783019</v>
+        <v>0.0365746007869771</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.021697018154415</v>
+        <v>-0.00795784228719191</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00122581591874153</v>
+        <v>0.000162435809123503</v>
       </c>
       <c r="H2" t="n">
-        <v>150</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3">
@@ -1220,25 +1220,25 @@
         <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.0000000210264724727155</v>
+        <v>-0.00000000888012577155734</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000000000953513918278973</v>
+        <v>0.000000000916710912743962</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.66017848036369</v>
+        <v>-2.31334580317817</v>
       </c>
       <c r="E3" t="n">
-        <v>0.102191894072722</v>
+        <v>0.0785834554637153</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0208419778075284</v>
+        <v>-0.0102535298477412</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00046721131160942</v>
+        <v>0.000348423686035674</v>
       </c>
       <c r="H3" t="n">
-        <v>465</v>
+        <v>635</v>
       </c>
     </row>
     <row r="4">
@@ -1246,25 +1246,25 @@
         <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.00000000929407698333992</v>
+        <v>-0.000000130113421703884</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000000000254458210773552</v>
+        <v>0.0000000146362689064322</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.81150424913892</v>
+        <v>-8.78303830624868</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0365746007869771</v>
+        <v>0.455536381185582</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.00795784228719191</v>
+        <v>-0.0403003279497853</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000162435809123503</v>
+        <v>0.00217898252389467</v>
       </c>
       <c r="H4" t="n">
-        <v>610</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -1272,25 +1272,25 @@
         <v>17</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.000000130113421703884</v>
+        <v>-0.0000000210264724727155</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0000000146362689064322</v>
+        <v>0.000000000953513918278973</v>
       </c>
       <c r="D5" t="n">
-        <v>-8.78303830624868</v>
+        <v>-4.66017848036369</v>
       </c>
       <c r="E5" t="n">
-        <v>0.455536381185582</v>
+        <v>0.102191894072722</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0403003279497853</v>
+        <v>-0.0208419778075284</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00217898252389467</v>
+        <v>0.00046721131160942</v>
       </c>
       <c r="H5" t="n">
-        <v>70</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6">
@@ -1298,25 +1298,25 @@
         <v>18</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.00000000888012577155734</v>
+        <v>-0.0000000261694186714065</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000000000916710912743962</v>
+        <v>0.00000000521578126918482</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.31334580317817</v>
+        <v>-4.81759411124543</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0785834554637153</v>
+        <v>0.262385940783019</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0102535298477412</v>
+        <v>-0.021697018154415</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000348423686035674</v>
+        <v>0.00122581591874153</v>
       </c>
       <c r="H6" t="n">
-        <v>635</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
